--- a/www/cost-template.xlsx
+++ b/www/cost-template.xlsx
@@ -1,36 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pathseattle-my.sharepoint.com/personal/jmillar_path_org/Documents/Documents/github_new/Personal/malaria-budgeting-tool/www/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pathseattle-my.sharepoint.com/personal/hthompson_path_org/Documents/Documents/github/malaria-budgeting-tool/www/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC1856BF-4AF3-4B95-A600-B84406414C6F}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15864844-53AA-44A9-9B9B-58E8B2A957BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
+    <workbookView xWindow="22695" yWindow="1905" windowWidth="25875" windowHeight="18375" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_cost_data" sheetId="1" r:id="rId1"/>
+    <sheet name="list-items-ignore" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
-  <si>
-    <t>resource</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>unit</t>
   </si>
   <si>
-    <t>ngn_cost</t>
-  </si>
-  <si>
     <t>usd_cost</t>
   </si>
   <si>
@@ -40,304 +35,181 @@
     <t>source</t>
   </si>
   <si>
-    <t>ITN Campaign-Procurement per ITN (Dual AI)</t>
-  </si>
-  <si>
-    <t>per ITN</t>
-  </si>
-  <si>
-    <t>ITN Campaign-Cost of distribution from State to LGA and from LGA to DHs</t>
-  </si>
-  <si>
-    <t>per bale</t>
-  </si>
-  <si>
-    <t>ITN Campaign-Operational cost per ITN</t>
-  </si>
-  <si>
-    <t>ITN Campaign-Storage of Hardwares</t>
-  </si>
-  <si>
-    <t>per year</t>
-  </si>
-  <si>
-    <t>ITN Routine Distribution-Pocurement cost per ITN (Dual AI)</t>
-  </si>
-  <si>
-    <t>ITN Routine Distribution-Operational cost per ITN</t>
-  </si>
-  <si>
-    <t>IRS-Cost per LGA</t>
-  </si>
-  <si>
-    <t>per lGA</t>
-  </si>
-  <si>
-    <t>LSM-Bti-Procurement cost per kg</t>
-  </si>
-  <si>
-    <t>per kg</t>
-  </si>
-  <si>
-    <t>LSM-Operational cost per LGA</t>
-  </si>
-  <si>
-    <t>per LGA</t>
-  </si>
-  <si>
-    <t>Malaria Vaccine-Procurement cost</t>
-  </si>
-  <si>
-    <t>per dose</t>
-  </si>
-  <si>
-    <t>Malaria Vaccine-Operational cost</t>
-  </si>
-  <si>
-    <t>per child</t>
-  </si>
-  <si>
-    <t>SMC-SPAQ-3-11 months-Procurement cost per SPAQ</t>
-  </si>
-  <si>
-    <t>per SPAQ</t>
-  </si>
-  <si>
-    <t>SMC-SPAQ-12-59 months-Procurement cost per SPAQ</t>
-  </si>
-  <si>
-    <t>SMC-Campaign cost per child</t>
-  </si>
-  <si>
-    <t>PMC-SP-Procurement cost</t>
-  </si>
-  <si>
-    <t>per SP</t>
-  </si>
-  <si>
-    <t>PMC-SP-Routine Distribution cost</t>
-  </si>
-  <si>
-    <t>IPTp-SP-Procurement cost per SP</t>
-  </si>
-  <si>
-    <t>IPTp-SP-Routine Distribution cost</t>
-  </si>
-  <si>
-    <t>Case Management-AL-Procurement cost per AL</t>
-  </si>
-  <si>
-    <t>per AL</t>
-  </si>
-  <si>
-    <t>Case Management-AL-Routine Distribution cost per AL</t>
-  </si>
-  <si>
-    <t>Case Management-Artesunate injections-Procurement cost</t>
-  </si>
-  <si>
-    <t>per 60mg powder</t>
-  </si>
-  <si>
-    <t>Case Management-Artesunate injections-Routine Distribution cost</t>
-  </si>
-  <si>
-    <t>Case Management-Rectal Artesunate Suppositories (RAS)-Procurement cost per RAS</t>
-  </si>
-  <si>
-    <t>per RAS</t>
-  </si>
-  <si>
-    <t>Case Management-RAS-Routine Distribution cost per RAS</t>
-  </si>
-  <si>
-    <t>Case Management-RDT kits-Procurement cost per kit &amp; consumables</t>
-  </si>
-  <si>
-    <t>per kit</t>
-  </si>
-  <si>
-    <t>Case Management-RDT kits-Distribution cost per kit &amp; consumables</t>
-  </si>
-  <si>
-    <t>Case Management-EQA cost per state</t>
-  </si>
-  <si>
-    <t>per state</t>
-  </si>
-  <si>
-    <t>NHMIS Tools Printing-Cost per health facility</t>
-  </si>
-  <si>
-    <t>per facility</t>
-  </si>
-  <si>
-    <t>NHMIS Tools Distribution-Cost per LGA</t>
-  </si>
-  <si>
-    <t>NMEP iMSV to States-Cost per State</t>
-  </si>
-  <si>
-    <t>per State</t>
-  </si>
-  <si>
-    <t>State and LGA M&amp;E Activities-Cost per LGA</t>
-  </si>
-  <si>
-    <t>NMEP Advocacy Visit to State Governors-Cost per state</t>
-  </si>
-  <si>
-    <t>Venue-Small hall-20 capacity in Abuja</t>
-  </si>
-  <si>
-    <t>per hall per day</t>
-  </si>
-  <si>
-    <t>Venue-Medium size hall-50 capacity in Abuja</t>
-  </si>
-  <si>
-    <t>Venue-Big hall-70 capacity in Abuja</t>
-  </si>
-  <si>
-    <t>Venue-Auditorium in Abuja</t>
-  </si>
-  <si>
-    <t>Venue-Small hall-20 capacity in state capital</t>
-  </si>
-  <si>
-    <t>Venue-Medium size hall-50 capacity in state capital</t>
-  </si>
-  <si>
-    <t>Venue-Big hall-70 capacity in state capital</t>
-  </si>
-  <si>
-    <t>Venue-Auditorium in state capital</t>
-  </si>
-  <si>
-    <t>Venue-Small hall-20 capacity in LGA</t>
-  </si>
-  <si>
-    <t>Venue-Medium size hall-50 capacity in LGA</t>
-  </si>
-  <si>
-    <t>Venue-Big hall-70 capacity in LGA</t>
-  </si>
-  <si>
-    <t>Venue-Auditorium in LGA</t>
-  </si>
-  <si>
-    <t>Training on malaria microscopy-Cost per person</t>
-  </si>
-  <si>
-    <t>per person</t>
-  </si>
-  <si>
-    <t>Training/workshop documents/materials</t>
-  </si>
-  <si>
-    <t>per unit</t>
-  </si>
-  <si>
-    <t>Photocopy of document-per page</t>
-  </si>
-  <si>
-    <t>per page</t>
-  </si>
-  <si>
-    <t>Printing of document-per page</t>
-  </si>
-  <si>
-    <t>Printing of booklets-Unit cost</t>
-  </si>
-  <si>
-    <t>Refreshments</t>
-  </si>
-  <si>
-    <t>per person per day</t>
-  </si>
-  <si>
-    <t>Tea break-Abuja</t>
-  </si>
-  <si>
-    <t>Tea break-State capital</t>
-  </si>
-  <si>
-    <t>Tea break-LGA</t>
-  </si>
-  <si>
-    <t>Lunch-Abuja</t>
-  </si>
-  <si>
-    <t>Lunch-State capital</t>
-  </si>
-  <si>
-    <t>Lunch-LGA</t>
-  </si>
-  <si>
-    <t>DSA-Abuja</t>
-  </si>
-  <si>
-    <t>per person per night</t>
-  </si>
-  <si>
-    <t>DSA-State capital</t>
-  </si>
-  <si>
-    <t>DSA-LGA</t>
-  </si>
-  <si>
-    <t>Stationery</t>
-  </si>
-  <si>
-    <t>Residential Workshop in Abuja-Cost per person per day</t>
-  </si>
-  <si>
-    <t>Non-residential Workshop in Abuja-Cost per person per day</t>
-  </si>
-  <si>
-    <t>Residential Workshop in State Capital-Cost per person per day</t>
-  </si>
-  <si>
-    <t>Non-residential Workshop in State Capital-Cost per person per day</t>
-  </si>
-  <si>
-    <t>Non-residential Workshop at LGA level-Cost per person per day</t>
-  </si>
-  <si>
-    <t>Flight ticket-Return within Nigeria</t>
-  </si>
-  <si>
-    <t>Airport Taxi (x4)</t>
-  </si>
-  <si>
-    <t>Travel-Ground-per km</t>
-  </si>
-  <si>
-    <t>Transport within state capital</t>
-  </si>
-  <si>
-    <t>Transport to and fro between LGAs and state capital</t>
-  </si>
-  <si>
-    <t>Transport within LGA</t>
-  </si>
-  <si>
-    <t>Advocacy kits</t>
-  </si>
-  <si>
-    <t>Facilitation fee-National</t>
-  </si>
-  <si>
-    <t>Facilitation fee-State</t>
-  </si>
-  <si>
-    <t>Facilitation fee-LGA</t>
-  </si>
-  <si>
-    <t>PMC-Cost per child per annum</t>
-  </si>
-  <si>
-    <t>Entomological Surveillance-Cost per state</t>
+    <t>resource_name</t>
+  </si>
+  <si>
+    <t>code_intervention</t>
+  </si>
+  <si>
+    <t>type_intervention</t>
+  </si>
+  <si>
+    <t>cost_class</t>
+  </si>
+  <si>
+    <t>local_currency_cost</t>
+  </si>
+  <si>
+    <t>cm_public</t>
+  </si>
+  <si>
+    <t>cm_private</t>
+  </si>
+  <si>
+    <t>iptp</t>
+  </si>
+  <si>
+    <t>smc</t>
+  </si>
+  <si>
+    <t>pmc</t>
+  </si>
+  <si>
+    <t>vacc</t>
+  </si>
+  <si>
+    <t>irs</t>
+  </si>
+  <si>
+    <t>lsm</t>
+  </si>
+  <si>
+    <t>itn_campaign</t>
+  </si>
+  <si>
+    <t>itn_routine</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>SP+AQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP+AS </t>
+  </si>
+  <si>
+    <t>AS+AQ</t>
+  </si>
+  <si>
+    <t>DHAP</t>
+  </si>
+  <si>
+    <t>RTSS</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>2GARD</t>
+  </si>
+  <si>
+    <t>Actellic 300CS</t>
+  </si>
+  <si>
+    <t>Bistar 10WP</t>
+  </si>
+  <si>
+    <t>FastM</t>
+  </si>
+  <si>
+    <t>Fendona 10 SC</t>
+  </si>
+  <si>
+    <t>Fendona 5 WP</t>
+  </si>
+  <si>
+    <t>Fendona 6 SC</t>
+  </si>
+  <si>
+    <t>Ficam</t>
+  </si>
+  <si>
+    <t>Fludora Fusion</t>
+  </si>
+  <si>
+    <t>ICON 10  CS - IRS</t>
+  </si>
+  <si>
+    <t>Icon WP</t>
+  </si>
+  <si>
+    <t>K-Othrine Polyzone</t>
+  </si>
+  <si>
+    <t>K-Othrine WG250</t>
+  </si>
+  <si>
+    <t>Klypson 500 WG</t>
+  </si>
+  <si>
+    <t>Lambda-cyhalothrin 10% WP</t>
+  </si>
+  <si>
+    <t>PALI 250 WG</t>
+  </si>
+  <si>
+    <t>Pendulum 10 SC</t>
+  </si>
+  <si>
+    <t>Pendulum 6 SC</t>
+  </si>
+  <si>
+    <t>REVIVAL 100 CS</t>
+  </si>
+  <si>
+    <t>REVIVAL 100 WP</t>
+  </si>
+  <si>
+    <t>RUBI 100 SC</t>
+  </si>
+  <si>
+    <t>RUBI 100 WP</t>
+  </si>
+  <si>
+    <t>RUBI 250 WG-SB</t>
+  </si>
+  <si>
+    <t>RUBI 50 SC</t>
+  </si>
+  <si>
+    <t>RUBI 50 WP</t>
+  </si>
+  <si>
+    <t>SOVRENTA 15WP</t>
+  </si>
+  <si>
+    <t>SumiShield 50WG</t>
+  </si>
+  <si>
+    <t>Sylando 240 SC</t>
+  </si>
+  <si>
+    <t>Vectron 20WP</t>
+  </si>
+  <si>
+    <t>VECTRON T500</t>
+  </si>
+  <si>
+    <t>Habitat Modification</t>
+  </si>
+  <si>
+    <t>Habitat Manipulation</t>
+  </si>
+  <si>
+    <t>Biological Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larviciding </t>
+  </si>
+  <si>
+    <t>Dual AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBO </t>
+  </si>
+  <si>
+    <t>Standard Pyrethroid</t>
   </si>
 </sst>
 </file>
@@ -1198,667 +1070,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CC70-95E1-4A45-9BAC-E2E83642FF0B}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="76.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{CF2B6038-255B-4E0E-9990-79C67B911883}">
+      <formula1>"Procurement, Distribution, Operational, Support, Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2B23E79F-74DE-47A3-AA72-02125CE1366C}">
+          <x14:formula1>
+            <xm:f>'list-items-ignore'!$B$1:$B$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5E138DD-4BA1-445F-A665-4841EF8F02BE}">
+          <x14:formula1>
+            <xm:f>'list-items-ignore'!$D$1:$D$44</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329D48F2-0C03-4D47-B72E-EFAD5BE6EF6C}">
+  <dimension ref="B1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
         <v>13</v>
       </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
         <v>14</v>
       </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
         <v>15</v>
       </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
         <v>31</v>
       </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
         <v>34</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
         <v>37</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
         <v>39</v>
       </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
         <v>40</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
         <v>42</v>
       </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
         <v>43</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
         <v>45</v>
       </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
         <v>46</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
         <v>48</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
         <v>50</v>
       </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
         <v>53</v>
       </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
         <v>54</v>
       </c>
-      <c r="B33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>55</v>
       </c>
-      <c r="B34" t="s">
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
         <v>57</v>
       </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
         <v>58</v>
       </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
         <v>59</v>
       </c>
-      <c r="B37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
         <v>60</v>
       </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
         <v>61</v>
       </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
         <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>83</v>
-      </c>
-      <c r="B57" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>84</v>
-      </c>
-      <c r="B58" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>87</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>88</v>
-      </c>
-      <c r="B61" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>89</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>91</v>
-      </c>
-      <c r="B64" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>95</v>
-      </c>
-      <c r="B68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>96</v>
-      </c>
-      <c r="B69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>97</v>
-      </c>
-      <c r="B70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>98</v>
-      </c>
-      <c r="B71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>100</v>
-      </c>
-      <c r="B73" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>101</v>
-      </c>
-      <c r="B74" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>102</v>
-      </c>
-      <c r="B75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>103</v>
-      </c>
-      <c r="B76" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>98</v>
-      </c>
-      <c r="B78" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>103</v>
-      </c>
-      <c r="B79" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>104</v>
-      </c>
-      <c r="B80" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>105</v>
-      </c>
-      <c r="B81" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/www/cost-template.xlsx
+++ b/www/cost-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pathseattle-my.sharepoint.com/personal/hthompson_path_org/Documents/Documents/github/malaria-budgeting-tool/www/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15864844-53AA-44A9-9B9B-58E8B2A957BB}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC33044-4127-4762-9905-AF801A4C0427}"/>
   <bookViews>
-    <workbookView xWindow="22695" yWindow="1905" windowWidth="25875" windowHeight="18375" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
+    <workbookView minimized="1" xWindow="7605" yWindow="1215" windowWidth="19860" windowHeight="15420" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_cost_data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>unit</t>
   </si>
@@ -33,9 +33,6 @@
   </si>
   <si>
     <t>source</t>
-  </si>
-  <si>
-    <t>resource_name</t>
   </si>
   <si>
     <t>code_intervention</t>
@@ -1070,18 +1067,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CC70-95E1-4A45-9BAC-E2E83642FF0B}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1092,27 +1088,24 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{CF2B6038-255B-4E0E-9990-79C67B911883}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{CF2B6038-255B-4E0E-9990-79C67B911883}">
       <formula1>"Procurement, Distribution, Operational, Support, Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1124,13 +1117,13 @@
           <x14:formula1>
             <xm:f>'list-items-ignore'!$B$1:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
+          <xm:sqref>A2:A1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5E138DD-4BA1-445F-A665-4841EF8F02BE}">
           <x14:formula1>
             <xm:f>'list-items-ignore'!$D$1:$D$44</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
+          <xm:sqref>B2:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1145,252 +1138,252 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/www/cost-template.xlsx
+++ b/www/cost-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pathseattle-my.sharepoint.com/personal/hthompson_path_org/Documents/Documents/github/malaria-budgeting-tool/www/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC33044-4127-4762-9905-AF801A4C0427}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A68DE36-8346-4F92-BBD6-702FF4F5064B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7605" yWindow="1215" windowWidth="19860" windowHeight="15420" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
+    <workbookView xWindow="28845" yWindow="630" windowWidth="21360" windowHeight="16035" activeTab="1" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_cost_data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="88">
   <si>
     <t>unit</t>
   </si>
@@ -44,9 +44,6 @@
     <t>cost_class</t>
   </si>
   <si>
-    <t>local_currency_cost</t>
-  </si>
-  <si>
     <t>cm_public</t>
   </si>
   <si>
@@ -207,6 +204,87 @@
   </si>
   <si>
     <t>Standard Pyrethroid</t>
+  </si>
+  <si>
+    <t>per ITN</t>
+  </si>
+  <si>
+    <t>per bale</t>
+  </si>
+  <si>
+    <t>per year</t>
+  </si>
+  <si>
+    <t>per State</t>
+  </si>
+  <si>
+    <t>per LGA</t>
+  </si>
+  <si>
+    <t>per child</t>
+  </si>
+  <si>
+    <t>per dose</t>
+  </si>
+  <si>
+    <t>per facility</t>
+  </si>
+  <si>
+    <t>per SP</t>
+  </si>
+  <si>
+    <t>per AL</t>
+  </si>
+  <si>
+    <t>per RDT kit</t>
+  </si>
+  <si>
+    <t>per RAS</t>
+  </si>
+  <si>
+    <t>per 60mg powder</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>Operational</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Net Storage</t>
+  </si>
+  <si>
+    <t>Campaign</t>
+  </si>
+  <si>
+    <t>per SPAQ pack 3-11 month olds</t>
+  </si>
+  <si>
+    <t>per SPAQ pack 12-59 month olds</t>
+  </si>
+  <si>
+    <t>ngn_cost</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Artesunate injections</t>
+  </si>
+  <si>
+    <t>RAS</t>
+  </si>
+  <si>
+    <t>RDT kits</t>
   </si>
 </sst>
 </file>
@@ -690,8 +768,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1067,40 +1146,422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CC70-95E1-4A45-9BAC-E2E83642FF0B}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="8" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1573,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2B23E79F-74DE-47A3-AA72-02125CE1366C}">
           <x14:formula1>
             <xm:f>'list-items-ignore'!$B$1:$B$10</xm:f>
@@ -1121,9 +1582,15 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E5E138DD-4BA1-445F-A665-4841EF8F02BE}">
           <x14:formula1>
-            <xm:f>'list-items-ignore'!$D$1:$D$44</xm:f>
+            <xm:f>'list-items-ignore'!$D:$D</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{613C0C3E-E487-435C-8D59-412773A42907}">
+          <x14:formula1>
+            <xm:f>'list-items-ignore'!$G:$G</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1133,257 +1600,332 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329D48F2-0C03-4D47-B72E-EFAD5BE6EF6C}">
-  <dimension ref="B1:D44"/>
+  <dimension ref="B1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="G4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="G6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="G7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D11" t="s">
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D14" t="s">
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
+      <c r="G15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D16" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/www/cost-template.xlsx
+++ b/www/cost-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pathseattle-my.sharepoint.com/personal/hthompson_path_org/Documents/Documents/github/malaria-budgeting-tool/www/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A68DE36-8346-4F92-BBD6-702FF4F5064B}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="8_{80C684BE-1432-4728-8906-CC0B9CE4E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B8C6A23-0949-41A1-A135-866A801AC0F1}"/>
   <bookViews>
-    <workbookView xWindow="28845" yWindow="630" windowWidth="21360" windowHeight="16035" activeTab="1" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
   </bookViews>
   <sheets>
     <sheet name="unit_cost_data" sheetId="1" r:id="rId1"/>
@@ -272,9 +272,6 @@
     <t>per SPAQ pack 12-59 month olds</t>
   </si>
   <si>
-    <t>ngn_cost</t>
-  </si>
-  <si>
     <t>AL</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>RDT kits</t>
+  </si>
+  <si>
+    <t>local_currency</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
         <v>74</v>
@@ -1463,7 +1463,7 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
         <v>75</v>
@@ -1477,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
         <v>74</v>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1505,7 +1505,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
         <v>74</v>
@@ -1519,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
         <v>75</v>
@@ -1533,7 +1533,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
         <v>74</v>
@@ -1547,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
         <v>75</v>
@@ -1910,22 +1910,22 @@
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
